--- a/www/download/COUNTRY.POL.WIOD16.xlsx
+++ b/www/download/COUNTRY.POL.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Polônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4.33926163816224</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>4.09200739174716</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>4.07829121268795</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>3.88745923269388</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>3.63876538246085</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3.23183627386198</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.10017073063648</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2.7579732051694</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>2.37751045900877</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>3.09695000909337</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>3.007035955218</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>2.94817875909032</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>3.25287701437415</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>3.15907559446081</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3.14829995833974</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>14.777</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>14.689</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>13.885</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>13.606</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>14.057</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>14.504</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>15.156</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15.732</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>15.789</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>15.37</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>15.457</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>15.475</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>15.464</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>15.572</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>10.601</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.347</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>9.891</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10.077</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>10.434</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10.948</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>11.593</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>12.152</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12.218</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>11.876</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>11.954</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>12.055</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>12.101</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>12.311</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>30998.699</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30957.757</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>29072.771</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>28387.481</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>28743.737</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>29246.32</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>30115.669</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>31356.249</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>32444.88</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>32228.957</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>31410.397</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>31414.157</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>31319.402</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>31276.043</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>31527.743</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22459.987</t>
+          <t>33749424958.4133</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21432.975</t>
+          <t>34593100181.5548</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20556.203</t>
+          <t>31646415145.3217</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20392.317</t>
+          <t>31665085882.1287</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20794.768</t>
+          <t>32420822902.3688</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>21478.274</t>
+          <t>33160448926.8559</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22538.087</t>
+          <t>34279975477.5909</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23853.77</t>
+          <t>35804520863.525</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24851.878</t>
+          <t>37667988454.7018</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>24823.243</t>
+          <t>36453875210.5583</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>24134.532</t>
+          <t>37470889854.8724</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24195.665</t>
+          <t>39188491819.4921</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24283.618</t>
+          <t>37938986068.1364</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>24309.245</t>
+          <t>37971929065.4575</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>24813.758</t>
+          <t>38220789699.8079</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7353551284.12591</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8041379237.46016</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6943121111.39288</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6686566800.43728</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6462308279.32439</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6604158844.08749</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6682682460.02708</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6998234869.15329</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>7844571944.77436</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>7085058645.30157</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>7171345633.0823</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>7276033865.10395</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7012473947.36348</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>7263450101.24057</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>7438655948.4522</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4632969.16796955</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4246674.33439814</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3959217.22652646</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3588501.05954333</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3062952.66255812</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2718077.66327716</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2469270.01725645</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2041780.1030178</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1755683.97530802</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2161114.40976916</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1982839.96176725</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1759859.74799099</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1858271.40972179</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1804872.27321612</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1764110.30085138</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>161153.44370596</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>162095.393084736</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>151339.922933047</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>163347.417560627</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>181921.183652177</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>198435.301477056</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>214248.538591939</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>247229.553947204</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>278855.194884229</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>246423.544552327</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>263094.018884809</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>279359.863489356</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>269362.521188002</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>270240.78471846</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>271017.93305235</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>274226.435662529</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>278439.645564394</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>256250.637668869</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>279041.276161324</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>315865.204561903</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>346874.247373849</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>378821.699050054</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>446736.414423073</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>510124.023793971</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>449267.581788946</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>511621.598539622</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>568230.116540166</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>536002.027254542</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>535934.226019191</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>541945.546722055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.05430480215516</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.665335680247</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.96065741475683</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.04974400295626</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.21785453450606</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.25223461565115</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.37261079436485</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2.40854093153436</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.16803493867565</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.50360445025553</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.36541190940016</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.32539202656038</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.46291739295945</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.3467903904025</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.33578514343887</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>25505.5372773167</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>27896.1533624624</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>29102.1570774225</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>32573.7795957501</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>35738.3230957667</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>40368.9988633374</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>43316.6206095945</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>54441.4415700064</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>66207.6725223462</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>54629.6988228424</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>60518.036940243</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>65474.4110249414</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>63294.4668848652</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>67899.4751570222</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>72670.6897127309</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.33926163816224</t>
+          <t>693.665813048383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.09200739174716</t>
+          <t>777.207677713252</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.07829121268795</t>
+          <t>695.668665036108</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.88745923269388</t>
+          <t>675.998018524908</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.63876538246085</t>
+          <t>641.286508948446</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.23183627386198</t>
+          <t>632.958159451733</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3.10017073063648</t>
+          <t>610.413275729104</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.7579732051694</t>
+          <t>603.676008967134</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.37751045900877</t>
+          <t>645.542832378012</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.09695000909337</t>
+          <t>579.867956958487</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3.007035955218</t>
+          <t>603.85193946466</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2.94817875909032</t>
+          <t>608.684663752976</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.25287701437415</t>
+          <t>581.697022642799</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3.15907559446081</t>
+          <t>600.245446684564</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3.14829995833974</t>
+          <t>604.238225659762</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-1416820986.98092</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-892963543.931088</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-770419238.336843</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>-838924263.169754</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-305335462.128522</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>67058196.4663855</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>160306202.565613</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>217362239.789838</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>368959686.131627</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>943285202.262785</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1321278369.15733</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>1710923433.43617</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>1754250627.15201</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>2790718216.4485</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>3177734736.44082</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>-1129009543.22173</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>-618879033.401091</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-424212970.75467</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>-323723440.120284</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>142964860.611477</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>549357805.853083</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>773639419.913699</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>705570691.033358</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1059945512.11074</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>325169966.611487</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>-309505429.941278</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>80929224.0419443</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>40387743.0179135</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>738715779.580695</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>935414276.534255</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>-287811443.759188</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>-274084510.529997</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>-346206267.582172</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>-515200823.04947</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>-448300322.739999</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-482299609.386698</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>-613333217.348086</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-488208451.24352</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>-690985825.979109</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>618115235.651298</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>1630783799.0986</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1629994209.39423</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>1713862884.1341</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>2052002436.86781</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>2242320459.90657</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>2118.66682388454</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>2071.51935437104</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>2059.63659135314</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>2061.62090300665</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>2063.56670073732</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>2058.52843642776</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>2058.68640274758</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>2057.65438594978</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>2045.10224738518</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>2031.62795456034</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2032.21050858875</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>2024.11512753373</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>2014.36873714248</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>2008.89569284675</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>2015.6088962537</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>2097.76671606179</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2107.51823594664</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>2093.79564233612</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>2086.37897765455</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>2088.88882707262</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>2080.55201438286</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>2076.38424574528</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>2068.91372094367</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>2062.36247065885</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>2041.17683327718</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>2043.57732680798</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>2032.31852098531</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2023.88394042076</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>2022.57207418131</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>2024.63012786134</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>45576.979435255</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50766.2542270721</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>55209.9049149072</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>69980.4901515183</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>86348.3837229576</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>104914.484962329</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>129394.936983058</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>163063.035668062</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>201268.315589185</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>160346.762484858</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>188781.605662927</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>221770.469924079</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>214610.319880977</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>234618.140674535</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>251641.573039011</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5735167727.84254</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5883872733.35843</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5751698348.6006</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6674503905.52167</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6819881921.06245</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>7347730360.20107</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7956495433.17584</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>8217645304.0149</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>8601360846.70059</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>7950395387.73405</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>7997928422.98042</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>8597514186.29645</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>8700213158.38624</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>9299533173.83081</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>9782081908.91282</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>55080.9791614594</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>55911.1078638065</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>59626.1154717151</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>72722.4779817281</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>87412.4737971808</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>102307.879947777</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>128670.891597609</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>169465.720928225</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>215990.793147171</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>155661.387639236</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>188388.156211291</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>222823.705640181</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>206290.176071694</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>215354.828977214</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>232567.054717117</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30998.699</t>
+          <t>5786723712.0614</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30957.757</t>
+          <t>5814548237.51631</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>29072.771</t>
+          <t>5694389204.04423</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28387.481</t>
+          <t>6252763724.69323</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28743.737</t>
+          <t>6661385554.14681</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>29246.32</t>
+          <t>7086116337.70343</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>30115.669</t>
+          <t>8033705152.3827</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>31356.249</t>
+          <t>9061194651.28352</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>32444.88</t>
+          <t>10237800474.8775</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>32228.957</t>
+          <t>8437560096.28238</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>31410.397</t>
+          <t>9285180190.11145</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>31414.157</t>
+          <t>10394854897.751</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>31319.402</t>
+          <t>9764482154.16527</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>31276.043</t>
+          <t>10483881834.8451</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>31527.743</t>
+          <t>11384717944.1409</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22459.987</t>
+          <t>-9503.99972620439</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21432.975</t>
+          <t>-5144.85363673431</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20556.203</t>
+          <t>-4416.21055680789</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20392.317</t>
+          <t>-2741.98783020978</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20794.768</t>
+          <t>-1064.09007422312</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21478.274</t>
+          <t>2606.60501455216</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>22538.087</t>
+          <t>724.045385449343</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23853.77</t>
+          <t>-6402.68526016364</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24851.878</t>
+          <t>-14722.4775579857</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>24823.243</t>
+          <t>4685.37484562144</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>24134.532</t>
+          <t>393.449451636447</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>24195.665</t>
+          <t>-1053.23571610209</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>24283.618</t>
+          <t>8320.14380928347</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24309.245</t>
+          <t>19263.311697321</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>24813.758</t>
+          <t>19074.5183218933</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>33750.295</t>
+          <t>-51555984.2188595</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>34594.954</t>
+          <t>69324495.8421199</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31648.578</t>
+          <t>57309144.5563682</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31666.728</t>
+          <t>421740180.828447</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>32421.205</t>
+          <t>158496366.915634</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>33160.93</t>
+          <t>261614022.497637</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>34281.138</t>
+          <t>-77209719.2068674</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>35807.874</t>
+          <t>-843549347.268622</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>37669.205</t>
+          <t>-1636439628.17692</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>36455.098</t>
+          <t>-487164708.548341</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>37474.727</t>
+          <t>-1287251767.13102</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>39193.447</t>
+          <t>-1797340711.45456</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>37940.84</t>
+          <t>-1064268995.77903</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>37971.611</t>
+          <t>-1184348661.01433</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>38218.247</t>
+          <t>-1602636035.22809</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>72670.7630404915</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>79186.4248886132</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>81243.3862046042</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>91003.2993276994</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>109694.519135625</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>129290.977875279</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>146952.580107273</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>183548.27636315</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>226766.180831549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>190190.503559029</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>203270.601551215</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>229938.395088067</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>215031.959355781</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>230290.257796619</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>236942.65066893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19833.376</t>
+          <t>0.136598736161724</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20138.591</t>
+          <t>0.129887305833836</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18690.162</t>
+          <t>0.142599602800088</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18536.362</t>
+          <t>0.147828940253508</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18672.631</t>
+          <t>0.182247725321745</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18969.998</t>
+          <t>0.192314406336786</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19387.576</t>
+          <t>0.207853928534669</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>19814.672</t>
+          <t>0.205574539307006</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>20590.903</t>
+          <t>0.194718822282648</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>19994.973</t>
+          <t>0.214414560636922</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>19268.864</t>
+          <t>0.207326091514599</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>19266.3</t>
+          <t>0.213452749728027</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19065.862</t>
+          <t>0.217912762906776</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>19147.058</t>
+          <t>0.214857702858467</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>19113.58</t>
+          <t>0.209162253429899</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>71154.2378036678</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>80656.4653655913</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>79865.145559256</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>85250.4738502308</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>94235.1602700566</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>112026.182488383</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>125289.986440234</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>156722.429475063</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>207016.948478951</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>165207.130321154</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>179859.835564439</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>194505.452790124</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>184004.736538528</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>195056.466998693</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>204113.582620104</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7353.776</t>
+          <t>85304.272748817</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8041.786</t>
+          <t>97785.4416775753</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6943.59</t>
+          <t>96177.8400751323</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6686.971</t>
+          <t>102118.522606331</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6462.394</t>
+          <t>112403.224672269</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>6604.295</t>
+          <t>132996.417001372</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6682.947</t>
+          <t>148756.228458876</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>6998.978</t>
+          <t>185640.448560253</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>7844.64</t>
+          <t>244635.665261069</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7085.288</t>
+          <t>196420.520884067</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>7172.008</t>
+          <t>212825.414697109</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>7276.904</t>
+          <t>232229.961189892</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>7012.765</t>
+          <t>217991.268495875</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>7263.445</t>
+          <t>231768.044826209</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>7438.142</t>
+          <t>241318.349447873</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>205.42</t>
+          <t>307313.953804102</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>166.52</t>
+          <t>340997.335679587</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>196.05</t>
+          <t>353479.913302993</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>204.96</t>
+          <t>385616.739707989</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>221.78</t>
+          <t>423034.383629644</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>489936.592558011</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>237.25</t>
+          <t>523846.516189478</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>240.82</t>
+          <t>658801.363701881</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>216.8</t>
+          <t>812273.123565822</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>250.35</t>
+          <t>650963.572485059</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>236.51</t>
+          <t>712105.196720569</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>232.5</t>
+          <t>775351.707819101</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>246.28</t>
+          <t>729179.511186234</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>234.68</t>
+          <t>780564.876396757</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>233.6</t>
+          <t>816429.916862391</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.633</t>
+          <t>123606.556696345</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.247</t>
+          <t>130640.722236737</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>125464.340091399</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>123852.815240217</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>117996.669846679</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>121000.684582854</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>125945.846111897</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>133513.445816151</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.756</t>
+          <t>145481.021394966</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>144575.896000144</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>147484.981303657</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>152186.322346309</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>152403.004579357</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>156398.781629049</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.764</t>
+          <t>161349.333783971</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>104058.484330882</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>109474.419618936</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>104658.059415567</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>103164.772337966</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>99619.858259317</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>102065.603966316</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>106217.004068049</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>113767.347751316</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>123344.019323254</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>121018.652216199</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>124640.331881694</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>128121.249986326</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>129495.35359728</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>132624.431274144</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>136812.688297263</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>67484.2349718195</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>72187.3785904003</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>79508.2523122386</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89579.0935707951</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>112835.377245156</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>134590.863803799</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>152200.176948777</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>189874.228407848</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>224372.538514931</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>194205.767207867</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>208156.024123553</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>230975.36506525</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>222191.98882247</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>235609.851431632</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>243437.010891254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>22459987000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>21432975000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20556203000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20392317000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>20794768000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>21478274000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>22538087000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23853770000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24851878000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>24823243000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>24134532000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>24195665000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>24283618000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>24309245000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>24813758000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>30998698763.2451</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30957756871.4674</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29072771252.9655</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>28387481007.8656</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>28743736927.1674</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>29246319666.1798</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>30115669461.865</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>31356249463.2502</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>32444880152.158</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>32228957491.3467</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>31410396586.2368</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>31414157074.4263</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>31319401589.6173</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>31276043269.1026</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>31527742814.0696</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>19833376173.2489</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20138591114.0013</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>18690162384.6458</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>18536361633.7923</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>18672631211.6492</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18969997714.5414</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>19387576444.1649</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19814672447.9898</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>20590902940.2526</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>19994972943.0377</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>19268864002.7087</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>19266299702.144</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19065862476.2563</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>19147058369.7251</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>19113579743.8022</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>14777000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14689200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13885200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13606100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>13760300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14057000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14503900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>15155900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>15731900</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15789400</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>15370300</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15457300</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>15474900</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>15463500</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>15572100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10601000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10346500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9980500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9891400</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10077100</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10433800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10947800</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>11592700</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12151900</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12218400</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>11876000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>11953700</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>12055200</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>12100800</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>12310800</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>30998698763.2451</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30957756871.4674</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>29072771252.9655</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>28387481007.8656</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>28743736927.1674</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>29246319666.1798</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>30115669461.865</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>31356249463.2502</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>32444880152.158</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>32228957491.3467</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>31410396586.2368</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>31414157074.4263</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>31319401589.6173</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>31276043269.1026</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>31527742814.0696</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>22459987000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>21432975000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20556203000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>20392317000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>20794768000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>21478274000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>22538087000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>23853770000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24851878000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>24823243000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>24134532000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24195665000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>24283618000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>24309245000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>24813758000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>334974.60193125</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>374552.868613436</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>384544.0803536</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>424463.27904</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>508946.375127</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>603394.775417</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>695532.495768</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>884827.945253</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1108469.481984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>873733.618187</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>960207.773196</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1083831.10569</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1012234.018928</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1060614.828234</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1105443.87064394</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>152788.830003739</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169973.552995028</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>175686.337390116</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>191697.61617</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>225238.629391</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>267587.2808</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>300956.405332</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>375514.676898</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>469008.203776</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>390626.25574</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>420981.438816</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>463205.32618</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>440183.226496</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>467377.959295</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>484755.614040083</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>458912.44874423</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>471391.584417544</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>462746.484875725</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>458058.040700495</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>443872.758859304</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>442181.305400447</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>440125.211597437</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>469602.390764688</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>473686.196077449</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>471095.526645914</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>493477.360765287</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>517567.576128434</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>520167.385827596</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>536012.825812482</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>551765.172614861</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
